--- a/Social charging model/charging_satisfaction_summary.xlsx
+++ b/Social charging model/charging_satisfaction_summary.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.692307692307692</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="C2" t="n">
-        <v>88.63929303514631</v>
+        <v>75.11317748193515</v>
       </c>
       <c r="D2" t="n">
-        <v>40.03950428415587</v>
+        <v>39.08286548175501</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>12.5</v>
       </c>
       <c r="C3" t="n">
-        <v>85.08306737582647</v>
+        <v>87.21962987323452</v>
       </c>
       <c r="D3" t="n">
-        <v>76.33610488677604</v>
+        <v>77.05016742017639</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +492,10 @@
         <v>9.090909090909092</v>
       </c>
       <c r="C4" t="n">
-        <v>88.00492926060745</v>
+        <v>85.93277203696752</v>
       </c>
       <c r="D4" t="n">
-        <v>71.1588080641254</v>
+        <v>65.37871816323236</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.692307692307692</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="C5" t="n">
-        <v>89.94321738516827</v>
+        <v>75.89571745568146</v>
       </c>
       <c r="D5" t="n">
-        <v>40.29332510135731</v>
+        <v>39.46615763157702</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.28571428571429</v>
+        <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>88.15907410538675</v>
+        <v>89.83249919685902</v>
       </c>
       <c r="D6" t="n">
-        <v>88.15907410538675</v>
+        <v>84.81442009206472</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         <v>12.5</v>
       </c>
       <c r="C7" t="n">
-        <v>87.07803508584608</v>
+        <v>84.61264299254535</v>
       </c>
       <c r="D7" t="n">
-        <v>78.95681347173027</v>
+        <v>76.854082553623</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.090909090909092</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>89.53267275816702</v>
+        <v>85.74738561376596</v>
       </c>
       <c r="D8" t="n">
-        <v>74.28823824637688</v>
+        <v>68.89150486809839</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.66666666666667</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="C9" t="n">
-        <v>86.33706528481468</v>
+        <v>88.48106558354905</v>
       </c>
       <c r="D9" t="n">
-        <v>90.27271577374452</v>
+        <v>88.48106558354905</v>
       </c>
     </row>
   </sheetData>
